--- a/_data_list/Field_Force_Sample_MO.xlsx
+++ b/_data_list/Field_Force_Sample_MO.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EMIL\OneDrive\Desktop\OrangeFlow\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Telegram_Project\OrangeFlow_Dev\_data_list\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EC6C1F5-0680-41F9-89E7-15D046C9B0AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D142DB42-56E1-4E18-9C61-73D3655C0170}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -257,9 +257,6 @@
     <t>BP</t>
   </si>
   <si>
-    <t>R291328</t>
-  </si>
-  <si>
     <t>Paeal Mia</t>
   </si>
   <si>
@@ -291,6 +288,9 @@
   </si>
   <si>
     <t>Md. Shahin Mia</t>
+  </si>
+  <si>
+    <t>R628535</t>
   </si>
 </sst>
 </file>
@@ -818,7 +818,7 @@
         <v>46</v>
       </c>
       <c r="C2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D2" t="s">
         <v>34</v>
@@ -868,7 +868,7 @@
         <v>47</v>
       </c>
       <c r="C3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D3" t="s">
         <v>34</v>
@@ -918,7 +918,7 @@
         <v>48</v>
       </c>
       <c r="C4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D4" t="s">
         <v>34</v>
@@ -968,7 +968,7 @@
         <v>49</v>
       </c>
       <c r="C5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D5" t="s">
         <v>34</v>
@@ -1018,7 +1018,7 @@
         <v>50</v>
       </c>
       <c r="C6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D6" t="s">
         <v>34</v>
@@ -1068,7 +1068,7 @@
         <v>51</v>
       </c>
       <c r="C7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D7" t="s">
         <v>34</v>
@@ -1162,13 +1162,13 @@
     </row>
     <row r="9" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D9" t="s">
         <v>72</v>
@@ -1180,7 +1180,7 @@
         <v>1999968844</v>
       </c>
       <c r="H9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K9" s="2">
         <v>45931</v>
@@ -1189,7 +1189,7 @@
         <v>31821</v>
       </c>
       <c r="O9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="P9" t="s">
         <v>35</v>
@@ -1212,7 +1212,7 @@
         <v>1935600928</v>
       </c>
       <c r="H10" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="K10" s="2"/>
       <c r="N10" s="2"/>
